--- a/CSS.xlsx
+++ b/CSS.xlsx
@@ -4,18 +4,19 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="css" sheetId="1" r:id="rId1"/>
     <sheet name="JS" sheetId="2" r:id="rId2"/>
+    <sheet name="css-topics" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="345" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="472" uniqueCount="347">
   <si>
     <t>Pseudo Class</t>
   </si>
@@ -422,9 +423,6 @@
     <t>Flexbox</t>
   </si>
   <si>
-    <t xml:space="preserve">vertically center or place items </t>
-  </si>
-  <si>
     <t xml:space="preserve">for horizontal placement of items </t>
   </si>
   <si>
@@ -452,9 +450,6 @@
     <t>Shrink items based on the no.</t>
   </si>
   <si>
-    <t>Grows items based on no.</t>
-  </si>
-  <si>
     <t>flex-basis</t>
   </si>
   <si>
@@ -473,9 +468,6 @@
     <t>flex-end, flex-start, center</t>
   </si>
   <si>
-    <t xml:space="preserve">position items within flexbox </t>
-  </si>
-  <si>
     <t xml:space="preserve">higher no.'s will be shown before the lower no.'s </t>
   </si>
   <si>
@@ -726,6 +718,345 @@
   </si>
   <si>
     <t>grid-template-rows</t>
+  </si>
+  <si>
+    <t>Inline, Internal &amp; External CSS &amp; where to use what</t>
+  </si>
+  <si>
+    <t>Class Selector (.class)</t>
+  </si>
+  <si>
+    <t>ID Selector(#ID)</t>
+  </si>
+  <si>
+    <t>Element Selector(div)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Child Selector (div&gt;p) where p is direct child </t>
+  </si>
+  <si>
+    <t>Decendent Selector (div p) where p is decendent and could be placed under any other child tag</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Universal Selector(*) this will apply to all the elements </t>
+  </si>
+  <si>
+    <t>Pseudo Class Selectors (refer to css sheet)</t>
+  </si>
+  <si>
+    <t>Content-&gt;Padding-&gt;Border-&gt;Margin</t>
+  </si>
+  <si>
+    <t>concept of margin collapse</t>
+  </si>
+  <si>
+    <t>Fonts (refer to css sheet, google fonts )</t>
+  </si>
+  <si>
+    <t>Text (refer to css sheet)</t>
+  </si>
+  <si>
+    <t>color (refer to css sheet)</t>
+  </si>
+  <si>
+    <t>text-decoration-color</t>
+  </si>
+  <si>
+    <t>text-decoration-style</t>
+  </si>
+  <si>
+    <t>add color to the text decoration</t>
+  </si>
+  <si>
+    <t>solid, dotted, double, wavy</t>
+  </si>
+  <si>
+    <t>text-decoration-thickness</t>
+  </si>
+  <si>
+    <t>adds indent to the text</t>
+  </si>
+  <si>
+    <t>text-overflow</t>
+  </si>
+  <si>
+    <t>overflow</t>
+  </si>
+  <si>
+    <t>word-break</t>
+  </si>
+  <si>
+    <t>break-all</t>
+  </si>
+  <si>
+    <t>decides what to do in case text is overflowing the box</t>
+  </si>
+  <si>
+    <t>hidden</t>
+  </si>
+  <si>
+    <t>whether to hide overflow or not</t>
+  </si>
+  <si>
+    <t xml:space="preserve">clip, ellipses, initial </t>
+  </si>
+  <si>
+    <t>whether to break the words or present them as full</t>
+  </si>
+  <si>
+    <t>color keywords, hex, rgb, rgba, hsl are mostly used</t>
+  </si>
+  <si>
+    <t>Specificity</t>
+  </si>
+  <si>
+    <t>Universal Selector(*) = 0</t>
+  </si>
+  <si>
+    <t>Element Selector=1</t>
+  </si>
+  <si>
+    <t>Class Selector=10</t>
+  </si>
+  <si>
+    <t>Attribute Selector=10</t>
+  </si>
+  <si>
+    <t>ID Selector=100</t>
+  </si>
+  <si>
+    <t>Inline=1000</t>
+  </si>
+  <si>
+    <t>important=10000</t>
+  </si>
+  <si>
+    <t>Cascade Algorithm</t>
+  </si>
+  <si>
+    <t>Sizing Units - px, rem, em, vh, vw, %, vmin, vmax</t>
+  </si>
+  <si>
+    <t>min-height</t>
+  </si>
+  <si>
+    <t>min-width</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>inline</t>
+  </si>
+  <si>
+    <t>block</t>
+  </si>
+  <si>
+    <t>inline-block</t>
+  </si>
+  <si>
+    <t>grid</t>
+  </si>
+  <si>
+    <t>box-shadow</t>
+  </si>
+  <si>
+    <t>Shadows &amp; outline</t>
+  </si>
+  <si>
+    <t>outline</t>
+  </si>
+  <si>
+    <t>outline-offset</t>
+  </si>
+  <si>
+    <t>Selectors</t>
+  </si>
+  <si>
+    <t>List Style</t>
+  </si>
+  <si>
+    <t>list-style-image</t>
+  </si>
+  <si>
+    <t>list-style(none, devanagari..etc)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">list-style-type </t>
+  </si>
+  <si>
+    <t>list-style-position (inside)</t>
+  </si>
+  <si>
+    <t>Overflow property</t>
+  </si>
+  <si>
+    <t>whitespace(nowrap-it keeps the text horrizontally)</t>
+  </si>
+  <si>
+    <t>text-overflow(ellipses-this will show the dots)</t>
+  </si>
+  <si>
+    <t>overflow(scroll, auto, clip)</t>
+  </si>
+  <si>
+    <t>overflow-x</t>
+  </si>
+  <si>
+    <t>overflow-y</t>
+  </si>
+  <si>
+    <t>overflow x y (shorthand)</t>
+  </si>
+  <si>
+    <t>Position(by default position is static)</t>
+  </si>
+  <si>
+    <t>z-index (it will work except with position static, it will stack the element in front or back)</t>
+  </si>
+  <si>
+    <t>top, bottom, left, right(it will work except with position static)</t>
+  </si>
+  <si>
+    <t>fixed (this will fix the element at the position  even if we scroll the page)</t>
+  </si>
+  <si>
+    <t>sticky(this is generally used for navbars, the element will behave like static till it reaches scroll but then sticks to it position and rest of the content will get scrolled under it)</t>
+  </si>
+  <si>
+    <t>Note: transform, filter, perspective properties can also make the element as positioned</t>
+  </si>
+  <si>
+    <t>relative(It will help move the position of the element while other elements remains static, so it can go over or stackup over other elements, its original position will remain preserved)</t>
+  </si>
+  <si>
+    <t>absolute(element takes position relative to the nearest positioned parent for top bottom left or right, its original position will not be preserved, other elements will move accordingly)</t>
+  </si>
+  <si>
+    <t>CSS Variables</t>
+  </si>
+  <si>
+    <t>Local Variable: .nav{--color: rgb; background-color: var(--color)}</t>
+  </si>
+  <si>
+    <t>Global Variable: first define the variable in the begining :root {--color: rgb1 ; --seccolor: rgb2 } then use it like .nav{background-color: var(--color); color: var(--seccolor); }</t>
+  </si>
+  <si>
+    <t>Media Queries</t>
+  </si>
+  <si>
+    <t>@media only screen and (max-width: 455px){body{background-color: blue;}}</t>
+  </si>
+  <si>
+    <t>@media only screen and (orientation: landscape){body{background-color: blue;}}</t>
+  </si>
+  <si>
+    <t>Float &amp; Clear</t>
+  </si>
+  <si>
+    <t>float(right, left)</t>
+  </si>
+  <si>
+    <t>display: flow-root; (this will stop the image overflow from container)</t>
+  </si>
+  <si>
+    <t>clear(right, left, both) if an element doesn’t need any image floating on its chosen side</t>
+  </si>
+  <si>
+    <t>Pseudo Class element (refer to css sheet)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vertically place items in center </t>
+  </si>
+  <si>
+    <t>align-content</t>
+  </si>
+  <si>
+    <t>When we have items in multiple lines</t>
+  </si>
+  <si>
+    <t>gap</t>
+  </si>
+  <si>
+    <t>sets gap between items, column-gap, row-gap can also be used</t>
+  </si>
+  <si>
+    <t>Takes spaces based on no. e.g if value is 2 then an item takes space of 2 items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">position single item within flexbox e.g one item is aligned on start, but rest are aligned in center. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">grid-row(start/end), row no. for start and end. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">grid-column(start/end), column no. for start and end. </t>
+  </si>
+  <si>
+    <t>grid-template-areas</t>
+  </si>
+  <si>
+    <t>grid-template-columns(100px 100px) or (1fr 2fr 1fr)</t>
+  </si>
+  <si>
+    <t>row-gap</t>
+  </si>
+  <si>
+    <t>column gap</t>
+  </si>
+  <si>
+    <t>justify-items(for all items)</t>
+  </si>
+  <si>
+    <t>align-items(for all items)</t>
+  </si>
+  <si>
+    <t>justify-self(for individual item)</t>
+  </si>
+  <si>
+    <t>align-self(for individual item)</t>
+  </si>
+  <si>
+    <t>grid-template-columns repeat(n, auto)</t>
+  </si>
+  <si>
+    <t>align-content (this apply to entire grid and if grid is smaller than the container)</t>
+  </si>
+  <si>
+    <t>justify-content (this apply to entire grid and if grid is smaller than the container)</t>
+  </si>
+  <si>
+    <t>place-content (it is combination of above two)</t>
+  </si>
+  <si>
+    <t>Transition property</t>
+  </si>
+  <si>
+    <t>Animations</t>
+  </si>
+  <si>
+    <t>object-fit(cover, contain)</t>
+  </si>
+  <si>
+    <t>object-position(top-right, bottom-left etc)</t>
+  </si>
+  <si>
+    <t>background-img: url()</t>
+  </si>
+  <si>
+    <t>background-position (center center)</t>
+  </si>
+  <si>
+    <t>background-repeat(no repeat, repeat-x, repeat-y)</t>
+  </si>
+  <si>
+    <t>Object fit property (used for images)</t>
+  </si>
+  <si>
+    <t>Filters (used for images)</t>
+  </si>
+  <si>
+    <t>filter (blurr(7px), contrast, brightness, invert, opacity etc)</t>
   </si>
 </sst>
 </file>
@@ -757,12 +1088,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -778,13 +1115,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1087,7 +1430,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H88"/>
+  <dimension ref="A1:H96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
@@ -1296,7 +1639,7 @@
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F20" s="1" t="s">
         <v>112</v>
@@ -1352,7 +1695,7 @@
         <v>131</v>
       </c>
       <c r="D24" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F24" s="1"/>
     </row>
@@ -1367,343 +1710,342 @@
         <v>133</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>316</v>
       </c>
       <c r="F25" s="1"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B26" t="s">
-        <v>137</v>
-      </c>
-      <c r="C26" t="s">
-        <v>138</v>
+        <v>317</v>
       </c>
       <c r="D26" t="s">
-        <v>140</v>
+        <v>318</v>
       </c>
       <c r="F26" s="1"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="B27" t="s">
-        <v>141</v>
+        <v>319</v>
       </c>
       <c r="C27" t="s">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="D27" t="s">
-        <v>145</v>
+        <v>320</v>
       </c>
       <c r="F27" s="1"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" t="s">
+        <v>137</v>
+      </c>
+      <c r="D28" t="s">
         <v>139</v>
-      </c>
-      <c r="B28" t="s">
-        <v>143</v>
-      </c>
-      <c r="C28" t="s">
-        <v>142</v>
-      </c>
-      <c r="D28" t="s">
-        <v>144</v>
       </c>
       <c r="F28" s="1"/>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B29" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="C29" t="s">
-        <v>74</v>
+        <v>141</v>
       </c>
       <c r="D29" t="s">
-        <v>147</v>
+        <v>321</v>
       </c>
       <c r="F29" s="1"/>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B30" t="s">
-        <v>122</v>
+        <v>142</v>
       </c>
       <c r="C30" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="D30" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F30" s="1"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B31" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>74</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="F31" s="1"/>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>122</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="D32" t="s">
-        <v>179</v>
+        <v>147</v>
       </c>
       <c r="F32" s="1"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>155</v>
+        <v>138</v>
       </c>
       <c r="B33" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C33" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="D33" t="s">
-        <v>161</v>
-      </c>
-      <c r="E33" t="s">
-        <v>180</v>
+        <v>322</v>
       </c>
       <c r="F33" s="1"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B34" t="s">
-        <v>236</v>
+        <v>153</v>
       </c>
       <c r="C34" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D34" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F34" s="1"/>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B35" t="s">
+        <v>153</v>
+      </c>
+      <c r="C35" t="s">
         <v>155</v>
       </c>
-      <c r="B35" t="s">
-        <v>164</v>
-      </c>
-      <c r="C35" t="s">
-        <v>163</v>
-      </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>158</v>
+      </c>
+      <c r="E35" t="s">
+        <v>177</v>
       </c>
       <c r="F35" s="1"/>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B36" t="s">
-        <v>159</v>
+        <v>233</v>
       </c>
       <c r="C36" t="s">
         <v>160</v>
       </c>
+      <c r="D36" t="s">
+        <v>162</v>
+      </c>
       <c r="F36" s="1"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B37" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="C37" t="s">
         <v>160</v>
       </c>
+      <c r="D37" t="s">
+        <v>163</v>
+      </c>
       <c r="F37" s="1"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B38" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="C38" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F38" s="1"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B39" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="C39" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="F39" s="1"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B40" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C40" t="s">
-        <v>138</v>
-      </c>
-      <c r="D40" t="s">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="F40" s="1"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B41" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="C41" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D41" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F41" s="1"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B42" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="C42" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D42" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="F42" s="1"/>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B43" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C43" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="D43" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F43" s="1"/>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B44" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C44" t="s">
-        <v>177</v>
+        <v>137</v>
       </c>
       <c r="D44" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="F44" s="1"/>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B45" t="s">
-        <v>181</v>
+        <v>172</v>
+      </c>
+      <c r="C45" t="s">
+        <v>174</v>
       </c>
       <c r="D45" t="s">
-        <v>183</v>
-      </c>
-      <c r="F45" s="1" t="s">
-        <v>185</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="F45" s="1"/>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="B46" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="C46" t="s">
-        <v>184</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>185</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="D46" t="s">
+        <v>175</v>
+      </c>
+      <c r="F46" s="1"/>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="B47" t="s">
-        <v>105</v>
-      </c>
-      <c r="C47" t="s">
-        <v>106</v>
+        <v>178</v>
       </c>
       <c r="D47" t="s">
-        <v>162</v>
+        <v>180</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>23</v>
+        <v>152</v>
       </c>
       <c r="B48" t="s">
-        <v>24</v>
+        <v>179</v>
       </c>
       <c r="C48" t="s">
-        <v>107</v>
-      </c>
-      <c r="D48" t="s">
-        <v>108</v>
+        <v>181</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>182</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
@@ -1711,13 +2053,13 @@
         <v>23</v>
       </c>
       <c r="B49" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="C49" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D49" t="s">
-        <v>108</v>
+        <v>159</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
@@ -1725,13 +2067,13 @@
         <v>23</v>
       </c>
       <c r="B50" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C50" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D50" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
@@ -1739,13 +2081,13 @@
         <v>23</v>
       </c>
       <c r="B51" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C51" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D51" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
@@ -1753,10 +2095,13 @@
         <v>23</v>
       </c>
       <c r="B52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>30</v>
+        <v>109</v>
+      </c>
+      <c r="D52" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -1764,10 +2109,13 @@
         <v>23</v>
       </c>
       <c r="B53" t="s">
-        <v>113</v>
+        <v>26</v>
       </c>
       <c r="C53" t="s">
-        <v>114</v>
+        <v>102</v>
+      </c>
+      <c r="D53" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -1775,10 +2123,10 @@
         <v>23</v>
       </c>
       <c r="B54" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
       <c r="C54" t="s">
-        <v>107</v>
+        <v>30</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -1786,49 +2134,46 @@
         <v>23</v>
       </c>
       <c r="B55" t="s">
-        <v>29</v>
+        <v>113</v>
       </c>
       <c r="C55" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B56" t="s">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="C56" t="s">
-        <v>37</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>36</v>
+        <v>107</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="B57" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="C57" t="s">
-        <v>47</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>44</v>
+        <v>116</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="B58" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C58" t="s">
-        <v>42</v>
+        <v>37</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
@@ -1836,10 +2181,13 @@
         <v>38</v>
       </c>
       <c r="B59" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C59" t="s">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
@@ -1847,7 +2195,7 @@
         <v>38</v>
       </c>
       <c r="B60" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C60" t="s">
         <v>42</v>
@@ -1855,30 +2203,24 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
-      </c>
-      <c r="E61" t="s">
-        <v>58</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>51</v>
+        <v>43</v>
+      </c>
+      <c r="C61" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B62" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
-      </c>
-      <c r="E62" t="s">
-        <v>58</v>
+        <v>42</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -1886,13 +2228,13 @@
         <v>49</v>
       </c>
       <c r="B63" t="s">
-        <v>56</v>
-      </c>
-      <c r="C63" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="E63" t="s">
         <v>58</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -1900,10 +2242,10 @@
         <v>49</v>
       </c>
       <c r="B64" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C64" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E64" t="s">
         <v>58</v>
@@ -1914,10 +2256,13 @@
         <v>49</v>
       </c>
       <c r="B65" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="C65" t="s">
-        <v>60</v>
+        <v>57</v>
+      </c>
+      <c r="E65" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -1925,10 +2270,13 @@
         <v>49</v>
       </c>
       <c r="B66" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="C66" t="s">
-        <v>62</v>
+        <v>55</v>
+      </c>
+      <c r="E66" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -1936,10 +2284,10 @@
         <v>49</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C67" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -1947,10 +2295,10 @@
         <v>49</v>
       </c>
       <c r="B68" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="C68" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -1958,38 +2306,32 @@
         <v>49</v>
       </c>
       <c r="B69" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="C69" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="B70" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>70</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="B71" t="s">
-        <v>72</v>
-      </c>
-      <c r="D71" t="s">
-        <v>84</v>
-      </c>
-      <c r="E71" t="s">
-        <v>83</v>
+        <v>66</v>
+      </c>
+      <c r="C71" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -1997,13 +2339,16 @@
         <v>86</v>
       </c>
       <c r="B72" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C72" t="s">
-        <v>74</v>
-      </c>
-      <c r="E72" t="s">
-        <v>83</v>
+        <v>70</v>
+      </c>
+      <c r="D72" t="s">
+        <v>262</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -2011,10 +2356,10 @@
         <v>86</v>
       </c>
       <c r="B73" t="s">
-        <v>75</v>
-      </c>
-      <c r="C73" t="s">
-        <v>76</v>
+        <v>72</v>
+      </c>
+      <c r="D73" t="s">
+        <v>84</v>
       </c>
       <c r="E73" t="s">
         <v>83</v>
@@ -2025,10 +2370,10 @@
         <v>86</v>
       </c>
       <c r="B74" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C74" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E74" t="s">
         <v>83</v>
@@ -2039,10 +2384,10 @@
         <v>86</v>
       </c>
       <c r="B75" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C75" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E75" t="s">
         <v>83</v>
@@ -2053,35 +2398,41 @@
         <v>86</v>
       </c>
       <c r="B76" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C76" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E76" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A77" t="s">
-        <v>85</v>
+      <c r="A77" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="B77" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="C77" t="s">
-        <v>88</v>
+        <v>80</v>
+      </c>
+      <c r="E77" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A78" t="s">
-        <v>85</v>
+      <c r="A78" s="3" t="s">
+        <v>86</v>
       </c>
       <c r="B78" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="C78" t="s">
-        <v>90</v>
+        <v>82</v>
+      </c>
+      <c r="E78" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
@@ -2089,10 +2440,10 @@
         <v>85</v>
       </c>
       <c r="B79" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C79" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
@@ -2100,10 +2451,10 @@
         <v>85</v>
       </c>
       <c r="B80" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="C80" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
@@ -2111,10 +2462,10 @@
         <v>85</v>
       </c>
       <c r="B81" t="s">
-        <v>95</v>
+        <v>247</v>
       </c>
       <c r="C81" t="s">
-        <v>96</v>
+        <v>249</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
@@ -2122,10 +2473,10 @@
         <v>85</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>248</v>
       </c>
       <c r="C82" t="s">
-        <v>98</v>
+        <v>250</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
@@ -2133,10 +2484,10 @@
         <v>85</v>
       </c>
       <c r="B83" t="s">
-        <v>99</v>
+        <v>251</v>
       </c>
       <c r="C83" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
@@ -2144,75 +2495,175 @@
         <v>85</v>
       </c>
       <c r="B84" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C84" t="s">
-        <v>102</v>
+        <v>92</v>
+      </c>
+      <c r="D84" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="B85" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="C85" t="s">
-        <v>120</v>
-      </c>
-      <c r="D85" t="s">
-        <v>121</v>
+        <v>94</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>117</v>
+        <v>85</v>
       </c>
       <c r="B86" t="s">
-        <v>119</v>
+        <v>253</v>
       </c>
       <c r="C86" t="s">
-        <v>142</v>
+        <v>260</v>
       </c>
       <c r="D86" t="s">
-        <v>153</v>
+        <v>257</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>186</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>187</v>
+        <v>85</v>
+      </c>
+      <c r="B87" t="s">
+        <v>254</v>
       </c>
       <c r="C87" t="s">
-        <v>188</v>
+        <v>258</v>
+      </c>
+      <c r="D87" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>190</v>
+        <v>85</v>
       </c>
       <c r="B88" t="s">
+        <v>255</v>
+      </c>
+      <c r="C88" t="s">
+        <v>256</v>
+      </c>
+      <c r="D88" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>85</v>
+      </c>
+      <c r="B89" t="s">
+        <v>95</v>
+      </c>
+      <c r="C89" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>85</v>
+      </c>
+      <c r="B90" t="s">
+        <v>97</v>
+      </c>
+      <c r="C90" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>85</v>
+      </c>
+      <c r="B91" t="s">
+        <v>99</v>
+      </c>
+      <c r="C91" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>85</v>
+      </c>
+      <c r="B92" t="s">
+        <v>101</v>
+      </c>
+      <c r="C92" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>117</v>
+      </c>
+      <c r="B93" t="s">
+        <v>118</v>
+      </c>
+      <c r="C93" t="s">
+        <v>120</v>
+      </c>
+      <c r="D93" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>117</v>
+      </c>
+      <c r="B94" t="s">
+        <v>119</v>
+      </c>
+      <c r="C94" t="s">
+        <v>141</v>
+      </c>
+      <c r="D94" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>183</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C95" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>187</v>
+      </c>
+      <c r="B96" t="s">
+        <v>186</v>
+      </c>
+      <c r="C96" s="5" t="s">
+        <v>188</v>
+      </c>
+      <c r="D96" t="s">
         <v>189</v>
-      </c>
-      <c r="C88" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="D88" t="s">
-        <v>192</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" location="pseudo-classes" display="https://learn.shayhowe.com/advanced-html-css/complex-selectors/ - pseudo-classes"/>
-    <hyperlink ref="F56" r:id="rId2" display="https://learn.shayhowe.com/advanced-html-css/css-transforms/"/>
-    <hyperlink ref="F57" r:id="rId3" display="https://learn.shayhowe.com/advanced-html-css/transitions-animations/"/>
-    <hyperlink ref="F61" r:id="rId4" location="background-color" display="https://learn.shayhowe.com/html-css/setting-backgrounds-and-gradients/ - background-color"/>
-    <hyperlink ref="F70" r:id="rId5" display="https://learn.shayhowe.com/html-css/working-with-typography/"/>
+    <hyperlink ref="F58" r:id="rId2" display="https://learn.shayhowe.com/advanced-html-css/css-transforms/"/>
+    <hyperlink ref="F59" r:id="rId3" display="https://learn.shayhowe.com/advanced-html-css/transitions-animations/"/>
+    <hyperlink ref="F63" r:id="rId4" location="background-color" display="https://learn.shayhowe.com/html-css/setting-backgrounds-and-gradients/ - background-color"/>
+    <hyperlink ref="F72" r:id="rId5" display="https://learn.shayhowe.com/html-css/working-with-typography/"/>
     <hyperlink ref="F20" r:id="rId6" display="https://learn.shayhowe.com/html-css/opening-the-box-model/"/>
-    <hyperlink ref="F45" r:id="rId7" display="https://www.youtube.com/watch?v=JBupsN9Cmrs&amp;list=PLu0W_9lII9agiCUZYRsvtGTXdxkzPyItg&amp;index=44"/>
-    <hyperlink ref="F46" r:id="rId8" display="https://www.youtube.com/watch?v=JBupsN9Cmrs&amp;list=PLu0W_9lII9agiCUZYRsvtGTXdxkzPyItg&amp;index=44"/>
+    <hyperlink ref="F47" r:id="rId7" display="https://www.youtube.com/watch?v=JBupsN9Cmrs&amp;list=PLu0W_9lII9agiCUZYRsvtGTXdxkzPyItg&amp;index=44"/>
+    <hyperlink ref="F48" r:id="rId8" display="https://www.youtube.com/watch?v=JBupsN9Cmrs&amp;list=PLu0W_9lII9agiCUZYRsvtGTXdxkzPyItg&amp;index=44"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
@@ -2236,161 +2687,724 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D2" t="s">
         <v>194</v>
       </c>
-      <c r="B2" t="s">
+      <c r="E2" t="s">
         <v>195</v>
-      </c>
-      <c r="C2" t="s">
-        <v>196</v>
-      </c>
-      <c r="D2" t="s">
-        <v>197</v>
-      </c>
-      <c r="E2" t="s">
-        <v>198</v>
       </c>
       <c r="F2" t="s">
         <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B6" t="s">
+        <v>202</v>
+      </c>
+      <c r="C6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D6" t="s">
         <v>204</v>
-      </c>
-      <c r="B6" t="s">
-        <v>205</v>
-      </c>
-      <c r="C6" t="s">
-        <v>206</v>
-      </c>
-      <c r="D6" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>206</v>
+      </c>
+      <c r="B8" t="s">
+        <v>207</v>
+      </c>
+      <c r="C8" t="s">
+        <v>208</v>
+      </c>
+      <c r="D8" t="s">
         <v>209</v>
-      </c>
-      <c r="B8" t="s">
-        <v>210</v>
-      </c>
-      <c r="C8" t="s">
-        <v>211</v>
-      </c>
-      <c r="D8" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B9" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>212</v>
+      </c>
+      <c r="B10" t="s">
+        <v>213</v>
+      </c>
+      <c r="C10" t="s">
+        <v>214</v>
+      </c>
+      <c r="D10" t="s">
         <v>215</v>
       </c>
-      <c r="B10" t="s">
+      <c r="E10" t="s">
         <v>216</v>
       </c>
-      <c r="C10" t="s">
+      <c r="F10" t="s">
         <v>217</v>
       </c>
-      <c r="D10" t="s">
+      <c r="G10" t="s">
         <v>218</v>
-      </c>
-      <c r="E10" t="s">
-        <v>219</v>
-      </c>
-      <c r="F10" t="s">
-        <v>220</v>
-      </c>
-      <c r="G10" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>219</v>
+      </c>
+      <c r="B11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" t="s">
+        <v>221</v>
+      </c>
+      <c r="D11" t="s">
         <v>222</v>
       </c>
-      <c r="B11" t="s">
+      <c r="E11" t="s">
         <v>223</v>
       </c>
-      <c r="C11" t="s">
+      <c r="F11" t="s">
         <v>224</v>
       </c>
-      <c r="D11" t="s">
+      <c r="G11" t="s">
         <v>225</v>
       </c>
-      <c r="E11" t="s">
+      <c r="H11" t="s">
         <v>226</v>
-      </c>
-      <c r="F11" t="s">
-        <v>227</v>
-      </c>
-      <c r="G11" t="s">
-        <v>228</v>
-      </c>
-      <c r="H11" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>227</v>
+      </c>
+      <c r="B12" t="s">
+        <v>228</v>
+      </c>
+      <c r="C12" t="s">
+        <v>229</v>
+      </c>
+      <c r="D12" t="s">
         <v>230</v>
       </c>
-      <c r="B12" t="s">
+      <c r="E12" t="s">
         <v>231</v>
       </c>
-      <c r="C12" t="s">
+      <c r="F12" t="s">
         <v>232</v>
-      </c>
-      <c r="D12" t="s">
-        <v>233</v>
-      </c>
-      <c r="E12" t="s">
-        <v>234</v>
-      </c>
-      <c r="F12" t="s">
-        <v>235</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D98"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="6">
+        <v>1</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6">
+        <v>2</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C3" s="6" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C4" s="6" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C5" s="6" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C6" s="6" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C7" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C8" s="6" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C9" s="3" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C10" s="3" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C11" s="3"/>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="6">
+        <v>3</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C13" s="6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C14" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C15" s="6" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="6">
+        <v>4</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C17" s="6" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C18" s="6" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="6">
+        <v>5</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C20" s="6" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C21" s="6" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C22" s="6" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C23" s="6" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C24" s="6" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C25" s="6" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C26" s="6" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" s="6" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="6">
+        <v>6</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C29" s="6" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C30" s="6" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="6">
+        <v>7</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C32" s="6" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C33" s="6" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C34" s="6" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C35" s="6" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C36" s="6" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="6">
+        <v>8</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C38" s="6" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C39" s="6" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C40" s="6" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C41" s="6" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A42" s="6">
+        <v>9</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C43" s="6" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C44" s="6" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C45" s="6" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C46" s="6" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" s="6">
+        <v>10</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C48" s="6" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C49" s="6" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C50" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C51" s="6" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C52" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C53" s="6" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A54" s="6">
+        <v>11</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C55" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C56" s="6" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C57" s="6" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C58" s="6" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C59" s="6" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C60" s="6" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C61" s="6" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A62" s="6">
+        <v>12</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C63" s="6" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C64" s="6" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A65" s="6">
+        <v>13</v>
+      </c>
+      <c r="B65" s="6" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C66" s="7" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C67" s="7" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A68" s="6">
+        <v>14</v>
+      </c>
+      <c r="B68" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C69" s="6" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C70" s="6" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C71" s="6" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A72" s="6">
+        <v>15</v>
+      </c>
+      <c r="B72" s="6" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C73" s="6" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C74" s="6" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C75" s="6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C76" s="6" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C77" s="6" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C78" s="6" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C79" s="6" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C80" s="6" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C81" s="6" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C82" s="6" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C83" t="s">
+        <v>333</v>
+      </c>
+      <c r="D83"/>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C84" s="6" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C85" s="6" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C86" s="6" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="6">
+        <v>16</v>
+      </c>
+      <c r="B87" s="6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="6">
+        <v>17</v>
+      </c>
+      <c r="B88" s="6" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="6">
+        <v>18</v>
+      </c>
+      <c r="B89" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="6">
+        <v>19</v>
+      </c>
+      <c r="B90" s="6" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C91" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C92" s="6" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C93" s="6" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C94" s="6" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C95" s="6" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C96" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="97" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A97" s="6">
+        <v>20</v>
+      </c>
+      <c r="B97" s="6" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="98" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C98" s="6" t="s">
+        <v>346</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>